--- a/Weekly_Scoreboard_Template.xlsx
+++ b/Weekly_Scoreboard_Template.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Head of Company" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Marketing" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer Success" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engineering" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finance" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Head of Company" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Marketing" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer Success" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Engineering" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finance" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +30,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +53,17 @@
       <i val="1"/>
       <color rgb="00808080"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00326AB5"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -82,8 +94,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -521,6 +542,335 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="104" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly Scoreboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>A worked example from a fictional company. It accompanies the article Scoreboard Day and</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>the Weekly Leadership Review at https://www.darlison.com/scoreboard-day/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>The Summary carries one row per Function: its Critical Number, and nothing else. Each</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Function then has its own tab holding the rest of the numbers it watches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Weeks run NEWEST FIRST, so this week is the far left column and history walks right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Every widget is two rows. The target is on top, the posted result underneath.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>THE COLOURS ARE RULES, NOT PAINT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Type a result under a target and the cell grades itself. Green at or past target, yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>within ten per cent, red beyond. Do not fill these cells by hand: a manual colour will sit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>on top of the rule and the board will start lying to you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>The Green / Red column states the band for each widget, so nobody has to guess what</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>earned a colour. Some widgets are better when LOWER, and read the other way round.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>A row marked monitor is watched but not graded. Tickets arriving and engineering capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>are neither good nor bad on their own; they are the input the graded numbers come from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>WHERE THE TARGETS COME FROM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Not from a judgment call at the start of the week. They come from the Approved column of</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>the 36 Month Rolling Financial Analysis, which ships with this file: take the Function's</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>number for the month and share it across that month's weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Share it by working days rather than by weeks, so a short week over a holiday is not asked</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>to do a full week's work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>And check whether the Critical Number is something the Function produces or something it</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>holds. Leads, closes and tickets are produced, so they divide across the month. A backlog,</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>a headcount or a cash reserve is held, so it does not divide: the weekly target is the</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>standard itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Do not take targets from the Rolling column. Rolling moves every month, so a forecast that</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>is drifting downwards would quietly lower the target and hide the miss you want to see.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>MAKING IT YOURS</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Put your own Functions down the left of the Summary and rename the Function tabs to match</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>your Functional Accountability Chart. Replace the week dates along the top. Then replace</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>the target rows with your own numbers. The colour rules follow automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>THE WEEKLY RHYTHM</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>1. Every owner posts their Critical Number by an agreed time on an agreed day. Ours was</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   10:00 on Thursday. The day does not matter. That it never moves does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2. Every red produces one written Situation Report: situation, cause, correction, and a</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   follow-up date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>3. The leadership meeting reviews the reds, confirms corrections, and routes anything too</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   complicated to settle in the room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>A number that stays red before its follow-up date does not earn another report. It already</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>has one, and the correction has until that date to work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>All numbers are fictional.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -541,89 +891,89 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Critical Number</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Green / Red</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>06-Mar</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>27-Feb</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>20-Feb</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>13-Feb</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>06-Feb</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>30-Jan</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>23-Jan</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>16-Jan</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>09-Jan</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>02-Jan</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Head of Company</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Reserve in Months</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -653,92 +1003,92 @@
           </r>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="J2" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="K2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="L2" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="N2" s="9" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="9" t="n">
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="12" t="n">
         <v>1.2</v>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="G3" s="12" t="n">
         <v>1.2</v>
       </c>
-      <c r="H3" s="9" t="n">
+      <c r="H3" s="12" t="n">
         <v>1.2</v>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="I3" s="12" t="n">
         <v>1.2</v>
       </c>
-      <c r="J3" s="9" t="n">
+      <c r="J3" s="12" t="n">
         <v>1.1</v>
       </c>
-      <c r="K3" s="9" t="n">
+      <c r="K3" s="12" t="n">
         <v>1.1</v>
       </c>
-      <c r="L3" s="9" t="n">
+      <c r="L3" s="12" t="n">
         <v>1.1</v>
       </c>
-      <c r="M3" s="9" t="n">
+      <c r="M3" s="12" t="n">
         <v>1.1</v>
       </c>
-      <c r="N3" s="9" t="n">
+      <c r="N3" s="12" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Marketing Qualified Leads</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -768,92 +1118,92 @@
           </r>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="H4" s="10" t="n">
+      <c r="H4" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="I4" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="J4" s="10" t="n">
+      <c r="J4" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="K4" s="10" t="n">
+      <c r="K4" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="L4" s="10" t="n">
+      <c r="L4" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="N4" s="10" t="n">
+      <c r="N4" s="13" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="11" t="n">
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="14" t="n">
         <v>29</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="J5" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="K5" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="L5" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="M5" s="11" t="n">
+      <c r="M5" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="N5" s="14" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>New Recurring Revenue Added</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -883,92 +1233,92 @@
           </r>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="15" t="n">
         <v>5208</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="15" t="n">
         <v>5714</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="15" t="n">
         <v>5714</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="15" t="n">
         <v>5714</v>
       </c>
-      <c r="I6" s="12" t="n">
+      <c r="I6" s="15" t="n">
         <v>5714</v>
       </c>
-      <c r="J6" s="12" t="n">
+      <c r="J6" s="15" t="n">
         <v>4750</v>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" s="15" t="n">
         <v>4750</v>
       </c>
-      <c r="L6" s="12" t="n">
+      <c r="L6" s="15" t="n">
         <v>4750</v>
       </c>
-      <c r="M6" s="12" t="n">
+      <c r="M6" s="15" t="n">
         <v>4750</v>
       </c>
-      <c r="N6" s="12" t="n">
+      <c r="N6" s="15" t="n">
         <v>3800</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="13" t="n">
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="16" t="n">
         <v>4800</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="16" t="n">
         <v>3600</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="16" t="n">
         <v>2400</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="I7" s="16" t="n">
         <v>2400</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="16" t="n">
         <v>4800</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K7" s="16" t="n">
         <v>4800</v>
       </c>
-      <c r="L7" s="13" t="n">
+      <c r="L7" s="16" t="n">
         <v>6000</v>
       </c>
-      <c r="M7" s="13" t="n">
+      <c r="M7" s="16" t="n">
         <v>4800</v>
       </c>
-      <c r="N7" s="13" t="n">
+      <c r="N7" s="16" t="n">
         <v>2400</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Customer Success</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Net Change in Existing Revenue</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -998,92 +1348,92 @@
           </r>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="15" t="n">
         <v>665</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="15" t="n">
         <v>708</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="15" t="n">
         <v>708</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="15" t="n">
         <v>708</v>
       </c>
-      <c r="I8" s="12" t="n">
+      <c r="I8" s="15" t="n">
         <v>708</v>
       </c>
-      <c r="J8" s="12" t="n">
+      <c r="J8" s="15" t="n">
         <v>571</v>
       </c>
-      <c r="K8" s="12" t="n">
+      <c r="K8" s="15" t="n">
         <v>571</v>
       </c>
-      <c r="L8" s="12" t="n">
+      <c r="L8" s="15" t="n">
         <v>571</v>
       </c>
-      <c r="M8" s="12" t="n">
+      <c r="M8" s="15" t="n">
         <v>571</v>
       </c>
-      <c r="N8" s="12" t="n">
+      <c r="N8" s="15" t="n">
         <v>457</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="13" t="n">
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="16" t="n">
         <v>672</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="16" t="n">
         <v>869</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="16" t="n">
         <v>364</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="I9" s="16" t="n">
         <v>928</v>
       </c>
-      <c r="J9" s="13" t="n">
+      <c r="J9" s="16" t="n">
         <v>591</v>
       </c>
-      <c r="K9" s="13" t="n">
+      <c r="K9" s="16" t="n">
         <v>579</v>
       </c>
-      <c r="L9" s="13" t="n">
+      <c r="L9" s="16" t="n">
         <v>522</v>
       </c>
-      <c r="M9" s="13" t="n">
+      <c r="M9" s="16" t="n">
         <v>596</v>
       </c>
-      <c r="N9" s="13" t="n">
+      <c r="N9" s="16" t="n">
         <v>453</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Tickets Resolved within SLA</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1113,92 +1463,92 @@
           </r>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="13" t="n">
         <v>71</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="13" t="n">
         <v>78</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="13" t="n">
         <v>78</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" s="13" t="n">
         <v>77</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I10" s="13" t="n">
         <v>77</v>
       </c>
-      <c r="J10" s="10" t="n">
+      <c r="J10" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="K10" s="10" t="n">
+      <c r="K10" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="L10" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="N10" s="10" t="n">
+      <c r="N10" s="13" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="11" t="n">
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="14" t="n">
         <v>78</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="14" t="n">
         <v>73</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="14" t="n">
         <v>79</v>
       </c>
-      <c r="J11" s="11" t="n">
+      <c r="J11" s="14" t="n">
         <v>64</v>
       </c>
-      <c r="K11" s="11" t="n">
+      <c r="K11" s="14" t="n">
         <v>63</v>
       </c>
-      <c r="L11" s="11" t="n">
+      <c r="L11" s="14" t="n">
         <v>64</v>
       </c>
-      <c r="M11" s="11" t="n">
+      <c r="M11" s="14" t="n">
         <v>63</v>
       </c>
-      <c r="N11" s="11" t="n">
+      <c r="N11" s="14" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Engineering</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Releases Shipped that Meet Acceptance</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1228,92 +1578,92 @@
           </r>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" s="10" t="n">
+      <c r="E12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" s="11" t="n">
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Cash Collected</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1343,77 +1693,77 @@
           </r>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="15" t="n">
         <v>238007</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="F14" s="15" t="n">
         <v>255386</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="G14" s="15" t="n">
         <v>255386</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="H14" s="15" t="n">
         <v>255386</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="I14" s="15" t="n">
         <v>255386</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="J14" s="15" t="n">
         <v>207500</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="K14" s="15" t="n">
         <v>207500</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="L14" s="15" t="n">
         <v>207500</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="M14" s="15" t="n">
         <v>207500</v>
       </c>
-      <c r="N14" s="12" t="n">
+      <c r="N14" s="15" t="n">
         <v>166000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="13" t="n">
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="16" t="n">
         <v>253426</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="16" t="n">
         <v>248201</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="16" t="n">
         <v>258651</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I15" s="16" t="n">
         <v>261264</v>
       </c>
-      <c r="J15" s="13" t="n">
+      <c r="J15" s="16" t="n">
         <v>207500</v>
       </c>
-      <c r="K15" s="13" t="n">
+      <c r="K15" s="16" t="n">
         <v>207500</v>
       </c>
-      <c r="L15" s="13" t="n">
+      <c r="L15" s="16" t="n">
         <v>207500</v>
       </c>
-      <c r="M15" s="13" t="n">
+      <c r="M15" s="16" t="n">
         <v>207500</v>
       </c>
-      <c r="N15" s="13" t="n">
+      <c r="N15" s="16" t="n">
         <v>166000</v>
       </c>
     </row>
@@ -1493,478 +1843,6 @@
     </cfRule>
     <cfRule type="expression" priority="21" dxfId="2" stopIfTrue="1">
       <formula>COUNT(F15,F14)=2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Widget</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Green / Red</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>06-Mar</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>27-Feb</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>20-Feb</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>13-Feb</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>06-Feb</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>30-Jan</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>23-Jan</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>16-Jan</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>09-Jan</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>02-Jan</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Head of Company</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Reserve in Months</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>≥ target</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  /  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>&gt; 10% below</t>
-          </r>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="I2" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="J2" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="K2" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="L2" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="M2" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="N2" s="6" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G3" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H3" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I3" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L3" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M3" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N3" s="9" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Growth Efficiency</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>≥ target</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  /  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>&gt; 10% below</t>
-          </r>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F4" s="14" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="G4" s="14" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="H4" s="14" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="I4" s="14" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="J4" s="14" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="K4" s="14" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="L4" s="14" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="M4" s="14" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N4" s="14" t="n">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="15" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="I5" s="15" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="J5" s="15" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="L5" s="15" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="M5" s="15" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="N5" s="15" t="n">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Rule of 40</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>≥ target</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  /  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>&gt; 10% below</t>
-          </r>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>0.362</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="I6" s="16" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="J6" s="16" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="K6" s="16" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="L6" s="16" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="M6" s="16" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="N6" s="16" t="n">
-        <v>0.347</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="17" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="G7" s="17" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="H7" s="17" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="I7" s="17" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="J7" s="17" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="K7" s="17" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="L7" s="17" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="M7" s="17" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="N7" s="17" t="n">
-        <v>0.347</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F3:N3">
-    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
-      <formula>AND(COUNT(F3,F2)=2,F3&gt;=F2)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
-      <formula>AND(COUNT(F3,F2)=2,F3&gt;=0.9*F2)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
-      <formula>COUNT(F3,F2)=2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:N5">
-    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="1">
-      <formula>AND(COUNT(F5,F4)=2,F5&gt;=F4)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
-      <formula>AND(COUNT(F5,F4)=2,F5&gt;=0.9*F4)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
-      <formula>COUNT(F5,F4)=2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:N7">
-    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
-      <formula>AND(COUNT(F7,F6)=2,F7&gt;=F6)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="8" dxfId="1" stopIfTrue="1">
-      <formula>AND(COUNT(F7,F6)=2,F7&gt;=0.9*F6)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
-      <formula>COUNT(F7,F6)=2</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1997,89 +1875,89 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Widget</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Green / Red</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>06-Mar</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>27-Feb</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>20-Feb</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>13-Feb</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>06-Feb</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>30-Jan</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>23-Jan</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>16-Jan</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>09-Jan</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>02-Jan</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Head of Company</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Reserve in Months</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2109,88 +1987,88 @@
           </r>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E2" s="10" t="n">
-        <v>1136</v>
-      </c>
-      <c r="F2" s="10" t="n">
-        <v>1250</v>
-      </c>
-      <c r="G2" s="10" t="n">
-        <v>1250</v>
-      </c>
-      <c r="H2" s="10" t="n">
-        <v>1250</v>
-      </c>
-      <c r="I2" s="10" t="n">
-        <v>1250</v>
-      </c>
-      <c r="J2" s="10" t="n">
-        <v>1042</v>
-      </c>
-      <c r="K2" s="10" t="n">
-        <v>1042</v>
-      </c>
-      <c r="L2" s="10" t="n">
-        <v>1042</v>
-      </c>
-      <c r="M2" s="10" t="n">
-        <v>1041</v>
-      </c>
-      <c r="N2" s="10" t="n">
-        <v>833</v>
+      <c r="E2" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G2" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="J2" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="K2" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="L2" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="M2" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="N2" s="9" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="11" t="n">
-        <v>1247</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>1272</v>
-      </c>
-      <c r="H3" s="11" t="n">
-        <v>1222</v>
-      </c>
-      <c r="I3" s="11" t="n">
-        <v>1259</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>1050</v>
-      </c>
-      <c r="K3" s="11" t="n">
-        <v>1081</v>
-      </c>
-      <c r="L3" s="11" t="n">
-        <v>1060</v>
-      </c>
-      <c r="M3" s="11" t="n">
-        <v>1070</v>
-      </c>
-      <c r="N3" s="11" t="n">
-        <v>839</v>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I3" s="12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J3" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K3" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L3" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M3" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N3" s="12" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Marketing Qualified Leads</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Growth Efficiency</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2220,88 +2098,88 @@
           </r>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E4" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="K4" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="L4" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="M4" s="10" t="n">
-        <v>25</v>
-      </c>
-      <c r="N4" s="10" t="n">
-        <v>20</v>
+      <c r="E4" s="17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J4" s="17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K4" s="17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L4" s="17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M4" s="17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N4" s="17" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="11" t="n">
-        <v>31</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="H5" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="K5" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="M5" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="N5" s="11" t="n">
-        <v>20</v>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="18" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L5" s="18" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M5" s="18" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="N5" s="18" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Sales Qualified Leads</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Rule of 40</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2331,78 +2209,78 @@
           </r>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="K6" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="L6" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="M6" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="N6" s="10" t="n">
-        <v>12</v>
+      <c r="E6" s="19" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="I6" s="19" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="L6" s="19" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="M6" s="19" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="N6" s="19" t="n">
+        <v>0.347</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="H7" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="K7" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="L7" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>12</v>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="20" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="H7" s="20" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="I7" s="20" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="J7" s="20" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="K7" s="20" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="L7" s="20" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="M7" s="20" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="N7" s="20" t="n">
+        <v>0.347</v>
       </c>
     </row>
   </sheetData>
@@ -2469,89 +2347,89 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Widget</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Green / Red</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>06-Mar</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>27-Feb</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>20-Feb</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>13-Feb</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>06-Feb</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>30-Jan</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>23-Jan</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>16-Jan</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>09-Jan</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>02-Jan</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Sales Qualified Leads Received</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2581,300 +2459,300 @@
           </r>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="E2" s="13" t="n">
+        <v>1136</v>
+      </c>
+      <c r="F2" s="13" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>1250</v>
+      </c>
+      <c r="H2" s="13" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I2" s="13" t="n">
+        <v>1250</v>
+      </c>
+      <c r="J2" s="13" t="n">
+        <v>1042</v>
+      </c>
+      <c r="K2" s="13" t="n">
+        <v>1042</v>
+      </c>
+      <c r="L2" s="13" t="n">
+        <v>1042</v>
+      </c>
+      <c r="M2" s="13" t="n">
+        <v>1041</v>
+      </c>
+      <c r="N2" s="13" t="n">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="14" t="n">
+        <v>1247</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>1272</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>1222</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>1259</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>1050</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>1081</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>1060</v>
+      </c>
+      <c r="M3" s="14" t="n">
+        <v>1070</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Marketing Qualified Leads</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>≥ target</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  /  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>&gt; 10% below</t>
+          </r>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="L4" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="M4" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="N4" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Sales Qualified Leads</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>≥ target</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  /  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>&gt; 10% below</t>
+          </r>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="F6" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="G6" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="H2" s="10" t="n">
+      <c r="H6" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="I2" s="10" t="n">
+      <c r="I6" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="J2" s="10" t="n">
+      <c r="J6" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="K2" s="10" t="n">
+      <c r="K6" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="L2" s="10" t="n">
+      <c r="L6" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="M2" s="10" t="n">
+      <c r="M6" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="N2" s="10" t="n">
+      <c r="N6" s="13" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="8" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="11" t="n">
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="G3" s="11" t="n">
+      <c r="G7" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="H3" s="11" t="n">
+      <c r="H7" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="I3" s="11" t="n">
+      <c r="I7" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="J3" s="11" t="n">
+      <c r="J7" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="K3" s="11" t="n">
+      <c r="K7" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="L3" s="11" t="n">
+      <c r="L7" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="M3" s="11" t="n">
+      <c r="M7" s="14" t="n">
         <v>16</v>
       </c>
-      <c r="N3" s="11" t="n">
+      <c r="N7" s="14" t="n">
         <v>12</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>New Customers Closed</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>≥ target</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  /  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>&gt; 10% below</t>
-          </r>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K4" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="N4" s="10" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" s="11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>New Recurring Revenue Added</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>≥ target</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  /  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>&gt; 10% below</t>
-          </r>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>5208</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>5714</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>5714</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>5714</v>
-      </c>
-      <c r="I6" s="12" t="n">
-        <v>5714</v>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>4750</v>
-      </c>
-      <c r="K6" s="12" t="n">
-        <v>4750</v>
-      </c>
-      <c r="L6" s="12" t="n">
-        <v>4750</v>
-      </c>
-      <c r="M6" s="12" t="n">
-        <v>4750</v>
-      </c>
-      <c r="N6" s="12" t="n">
-        <v>3800</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="13" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>3600</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>2400</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>2400</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>4800</v>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>4800</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>6000</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>4800</v>
-      </c>
-      <c r="N7" s="13" t="n">
-        <v>2400</v>
       </c>
     </row>
   </sheetData>
@@ -2916,6 +2794,478 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Widget</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Green / Red</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>06-Mar</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>27-Feb</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>20-Feb</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>13-Feb</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>06-Feb</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>30-Jan</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>23-Jan</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>16-Jan</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>09-Jan</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>02-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Sales Qualified Leads Received</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>≥ target</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  /  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>&gt; 10% below</t>
+          </r>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="F2" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="H2" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="I2" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="J2" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="K2" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="L2" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="M2" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="N2" s="13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="M3" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>New Customers Closed</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>≥ target</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  /  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>&gt; 10% below</t>
+          </r>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>New Recurring Revenue Added</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>≥ target</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  /  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>&gt; 10% below</t>
+          </r>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>5208</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>5714</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>5714</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>5714</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>5714</v>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>4750</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>4750</v>
+      </c>
+      <c r="L6" s="15" t="n">
+        <v>4750</v>
+      </c>
+      <c r="M6" s="15" t="n">
+        <v>4750</v>
+      </c>
+      <c r="N6" s="15" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="16" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>3600</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>2400</v>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>4800</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>4800</v>
+      </c>
+      <c r="L7" s="16" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M7" s="16" t="n">
+        <v>4800</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F3:N3">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>AND(COUNT(F3,F2)=2,F3&gt;=F2)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
+      <formula>AND(COUNT(F3,F2)=2,F3&gt;=0.9*F2)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>COUNT(F3,F2)=2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:N5">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="1">
+      <formula>AND(COUNT(F5,F4)=2,F5&gt;=F4)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
+      <formula>AND(COUNT(F5,F4)=2,F5&gt;=0.9*F4)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
+      <formula>COUNT(F5,F4)=2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:N7">
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>AND(COUNT(F7,F6)=2,F7&gt;=F6)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="1" stopIfTrue="1">
+      <formula>AND(COUNT(F7,F6)=2,F7&gt;=0.9*F6)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
+      <formula>COUNT(F7,F6)=2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2941,89 +3291,89 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Widget</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Green / Red</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>06-Mar</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>27-Feb</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>20-Feb</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>13-Feb</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>06-Feb</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>30-Jan</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>23-Jan</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>16-Jan</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>09-Jan</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>02-Jan</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Customer Success</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Expansion Revenue</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3053,88 +3403,88 @@
           </r>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E2" s="12" t="n">
+      <c r="E2" s="15" t="n">
         <v>2856</v>
       </c>
-      <c r="F2" s="12" t="n">
+      <c r="F2" s="15" t="n">
         <v>3065</v>
       </c>
-      <c r="G2" s="12" t="n">
+      <c r="G2" s="15" t="n">
         <v>3065</v>
       </c>
-      <c r="H2" s="12" t="n">
+      <c r="H2" s="15" t="n">
         <v>3065</v>
       </c>
-      <c r="I2" s="12" t="n">
+      <c r="I2" s="15" t="n">
         <v>3065</v>
       </c>
-      <c r="J2" s="12" t="n">
+      <c r="J2" s="15" t="n">
         <v>2490</v>
       </c>
-      <c r="K2" s="12" t="n">
+      <c r="K2" s="15" t="n">
         <v>2490</v>
       </c>
-      <c r="L2" s="12" t="n">
+      <c r="L2" s="15" t="n">
         <v>2490</v>
       </c>
-      <c r="M2" s="12" t="n">
+      <c r="M2" s="15" t="n">
         <v>2490</v>
       </c>
-      <c r="N2" s="12" t="n">
+      <c r="N2" s="15" t="n">
         <v>1992</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="13" t="n">
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="16" t="n">
         <v>3034</v>
       </c>
-      <c r="G3" s="13" t="n">
+      <c r="G3" s="16" t="n">
         <v>3127</v>
       </c>
-      <c r="H3" s="13" t="n">
+      <c r="H3" s="16" t="n">
         <v>3003</v>
       </c>
-      <c r="I3" s="13" t="n">
+      <c r="I3" s="16" t="n">
         <v>3096</v>
       </c>
-      <c r="J3" s="13" t="n">
+      <c r="J3" s="16" t="n">
         <v>2504</v>
       </c>
-      <c r="K3" s="13" t="n">
+      <c r="K3" s="16" t="n">
         <v>2480</v>
       </c>
-      <c r="L3" s="13" t="n">
+      <c r="L3" s="16" t="n">
         <v>2455</v>
       </c>
-      <c r="M3" s="13" t="n">
+      <c r="M3" s="16" t="n">
         <v>2529</v>
       </c>
-      <c r="N3" s="13" t="n">
+      <c r="N3" s="16" t="n">
         <v>1984</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Contraction Revenue</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3164,88 +3514,88 @@
           </r>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="15" t="n">
         <v>714</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="15" t="n">
         <v>766</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="15" t="n">
         <v>766</v>
       </c>
-      <c r="H4" s="12" t="n">
+      <c r="H4" s="15" t="n">
         <v>766</v>
       </c>
-      <c r="I4" s="12" t="n">
+      <c r="I4" s="15" t="n">
         <v>766</v>
       </c>
-      <c r="J4" s="12" t="n">
+      <c r="J4" s="15" t="n">
         <v>622</v>
       </c>
-      <c r="K4" s="12" t="n">
+      <c r="K4" s="15" t="n">
         <v>622</v>
       </c>
-      <c r="L4" s="12" t="n">
+      <c r="L4" s="15" t="n">
         <v>622</v>
       </c>
-      <c r="M4" s="12" t="n">
+      <c r="M4" s="15" t="n">
         <v>622</v>
       </c>
-      <c r="N4" s="12" t="n">
+      <c r="N4" s="15" t="n">
         <v>498</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="13" t="n">
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="16" t="n">
         <v>771</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="16" t="n">
         <v>736</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="16" t="n">
         <v>842</v>
       </c>
-      <c r="I5" s="13" t="n">
+      <c r="I5" s="16" t="n">
         <v>715</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="16" t="n">
         <v>613</v>
       </c>
-      <c r="K5" s="13" t="n">
+      <c r="K5" s="16" t="n">
         <v>625</v>
       </c>
-      <c r="L5" s="13" t="n">
+      <c r="L5" s="16" t="n">
         <v>631</v>
       </c>
-      <c r="M5" s="13" t="n">
+      <c r="M5" s="16" t="n">
         <v>619</v>
       </c>
-      <c r="N5" s="13" t="n">
+      <c r="N5" s="16" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Churned Revenue</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3275,88 +3625,88 @@
           </r>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="15" t="n">
         <v>1477</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="15" t="n">
         <v>1590</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="15" t="n">
         <v>1590</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="15" t="n">
         <v>1590</v>
       </c>
-      <c r="I6" s="12" t="n">
+      <c r="I6" s="15" t="n">
         <v>1590</v>
       </c>
-      <c r="J6" s="12" t="n">
+      <c r="J6" s="15" t="n">
         <v>1296</v>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" s="15" t="n">
         <v>1296</v>
       </c>
-      <c r="L6" s="12" t="n">
+      <c r="L6" s="15" t="n">
         <v>1296</v>
       </c>
-      <c r="M6" s="12" t="n">
+      <c r="M6" s="15" t="n">
         <v>1296</v>
       </c>
-      <c r="N6" s="12" t="n">
+      <c r="N6" s="15" t="n">
         <v>1037</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="13" t="n">
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="16" t="n">
         <v>1590</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="16" t="n">
         <v>1521</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="16" t="n">
         <v>1798</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="I7" s="16" t="n">
         <v>1452</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="16" t="n">
         <v>1301</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K7" s="16" t="n">
         <v>1275</v>
       </c>
-      <c r="L7" s="13" t="n">
+      <c r="L7" s="16" t="n">
         <v>1301</v>
       </c>
-      <c r="M7" s="13" t="n">
+      <c r="M7" s="16" t="n">
         <v>1314</v>
       </c>
-      <c r="N7" s="13" t="n">
+      <c r="N7" s="16" t="n">
         <v>1030</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Net Change in Existing Revenue</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3386,88 +3736,88 @@
           </r>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="15" t="n">
         <v>665</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="15" t="n">
         <v>708</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="15" t="n">
         <v>708</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="15" t="n">
         <v>708</v>
       </c>
-      <c r="I8" s="12" t="n">
+      <c r="I8" s="15" t="n">
         <v>708</v>
       </c>
-      <c r="J8" s="12" t="n">
+      <c r="J8" s="15" t="n">
         <v>571</v>
       </c>
-      <c r="K8" s="12" t="n">
+      <c r="K8" s="15" t="n">
         <v>571</v>
       </c>
-      <c r="L8" s="12" t="n">
+      <c r="L8" s="15" t="n">
         <v>571</v>
       </c>
-      <c r="M8" s="12" t="n">
+      <c r="M8" s="15" t="n">
         <v>571</v>
       </c>
-      <c r="N8" s="12" t="n">
+      <c r="N8" s="15" t="n">
         <v>457</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="13" t="n">
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="16" t="n">
         <v>672</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="16" t="n">
         <v>869</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="16" t="n">
         <v>364</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="I9" s="16" t="n">
         <v>928</v>
       </c>
-      <c r="J9" s="13" t="n">
+      <c r="J9" s="16" t="n">
         <v>591</v>
       </c>
-      <c r="K9" s="13" t="n">
+      <c r="K9" s="16" t="n">
         <v>579</v>
       </c>
-      <c r="L9" s="13" t="n">
+      <c r="L9" s="16" t="n">
         <v>522</v>
       </c>
-      <c r="M9" s="13" t="n">
+      <c r="M9" s="16" t="n">
         <v>596</v>
       </c>
-      <c r="N9" s="13" t="n">
+      <c r="N9" s="16" t="n">
         <v>453</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Customers Lost</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3497,77 +3847,77 @@
           </r>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="10" t="n">
+      <c r="E10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" s="10" t="n">
+      <c r="G10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="11" t="n">
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" s="11" t="n">
+      <c r="G11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3625,572 +3975,6 @@
     </cfRule>
     <cfRule type="expression" priority="15" dxfId="2" stopIfTrue="1">
       <formula>COUNT(F11,F10)=2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Widget</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Green / Red</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>06-Mar</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>27-Feb</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>20-Feb</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>13-Feb</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>06-Feb</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>30-Jan</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>23-Jan</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>16-Jan</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>09-Jan</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>02-Jan</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Tickets Received</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <i val="1"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t>not graded</t>
-          </r>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="n">
-        <v>78</v>
-      </c>
-      <c r="F2" s="10" t="n">
-        <v>85</v>
-      </c>
-      <c r="G2" s="10" t="n">
-        <v>84</v>
-      </c>
-      <c r="H2" s="10" t="n">
-        <v>84</v>
-      </c>
-      <c r="I2" s="10" t="n">
-        <v>84</v>
-      </c>
-      <c r="J2" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="K2" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="L2" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="M2" s="10" t="n">
-        <v>69</v>
-      </c>
-      <c r="N2" s="10" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>monitor</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="11" t="n">
-        <v>83</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <v>84</v>
-      </c>
-      <c r="H3" s="11" t="n">
-        <v>87</v>
-      </c>
-      <c r="I3" s="11" t="n">
-        <v>83</v>
-      </c>
-      <c r="J3" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="K3" s="11" t="n">
-        <v>68</v>
-      </c>
-      <c r="L3" s="11" t="n">
-        <v>70</v>
-      </c>
-      <c r="M3" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="N3" s="11" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Tickets Resolved within SLA</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>≥ target</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  /  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>&gt; 10% below</t>
-          </r>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>71</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>78</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <v>78</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>77</v>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>77</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="K4" s="10" t="n">
-        <v>64</v>
-      </c>
-      <c r="L4" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="M4" s="10" t="n">
-        <v>63</v>
-      </c>
-      <c r="N4" s="10" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>78</v>
-      </c>
-      <c r="H5" s="11" t="n">
-        <v>73</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>79</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>64</v>
-      </c>
-      <c r="K5" s="11" t="n">
-        <v>63</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>64</v>
-      </c>
-      <c r="M5" s="11" t="n">
-        <v>63</v>
-      </c>
-      <c r="N5" s="11" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Tickets Unresolved</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>≤ target</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  /  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>&gt; 10% above</t>
-          </r>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="K6" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="M6" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="N6" s="10" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K7" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Customers with an Unresolved Issue</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="001E7B34"/>
-              <sz val="10"/>
-            </rPr>
-            <t>≤ target</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <color rgb="00808080"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">  /  </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Arial"/>
-              <b val="1"/>
-              <color rgb="00C00000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>&gt; 10% above</t>
-          </r>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K8" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="M8" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="N8" s="10" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M9" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="N9" s="11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F5:N5">
-    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
-      <formula>AND(COUNT(F5,F4)=2,F5&gt;=F4)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
-      <formula>AND(COUNT(F5,F4)=2,F5&gt;=0.9*F4)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
-      <formula>COUNT(F5,F4)=2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:N7">
-    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="1">
-      <formula>AND(COUNT(F7,F6)=2,F7&lt;=F6)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
-      <formula>AND(COUNT(F7,F6)=2,F7&lt;=1.1*F6)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
-      <formula>COUNT(F7,F6)=2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9:N9">
-    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
-      <formula>AND(COUNT(F9,F8)=2,F9&lt;=F8)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="8" dxfId="1" stopIfTrue="1">
-      <formula>AND(COUNT(F9,F8)=2,F9&lt;=1.1*F8)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
-      <formula>COUNT(F9,F8)=2</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4223,89 +4007,89 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Widget</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Green / Red</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>06-Mar</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>27-Feb</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>20-Feb</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>13-Feb</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>06-Feb</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>30-Jan</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>23-Jan</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>16-Jan</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>09-Jan</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>02-Jan</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Engineering</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Development Capacity</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Tickets Received</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4318,88 +4102,88 @@
           </r>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E2" s="18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="F2" s="18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G2" s="18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H2" s="18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I2" s="18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J2" s="18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K2" s="18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L2" s="18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M2" s="18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N2" s="18" t="n">
-        <v>4.3</v>
+      <c r="E2" s="13" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="H2" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="I2" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="J2" s="13" t="n">
+        <v>69</v>
+      </c>
+      <c r="K2" s="13" t="n">
+        <v>69</v>
+      </c>
+      <c r="L2" s="13" t="n">
+        <v>69</v>
+      </c>
+      <c r="M2" s="13" t="n">
+        <v>69</v>
+      </c>
+      <c r="N2" s="13" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>monitor</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G3" s="19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H3" s="19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I3" s="19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J3" s="19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K3" s="19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L3" s="19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="M3" s="19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N3" s="19" t="n">
-        <v>4.3</v>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>84</v>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>87</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>69</v>
+      </c>
+      <c r="K3" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="L3" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="M3" s="14" t="n">
+        <v>69</v>
+      </c>
+      <c r="N3" s="14" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Releases Shipped that Meet Acceptance</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Tickets Resolved within SLA</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4429,88 +4213,88 @@
           </r>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="10" t="n">
-        <v>0</v>
+      <c r="E4" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>78</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>78</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="L4" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="M4" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="N4" s="13" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="11" t="n">
-        <v>0</v>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>73</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>51</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Product Releases</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Tickets Unresolved</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4519,7 +4303,7 @@
               <color rgb="001E7B34"/>
               <sz val="10"/>
             </rPr>
-            <t>≥ target</t>
+            <t>≤ target</t>
           </r>
           <r>
             <rPr>
@@ -4536,92 +4320,92 @@
               <color rgb="00C00000"/>
               <sz val="10"/>
             </rPr>
-            <t>&gt; 10% below</t>
-          </r>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+            <t>&gt; 10% above</t>
+          </r>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="10" t="n">
-        <v>0</v>
+      <c r="E6" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="N6" s="13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>0</v>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" s="14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Quality Releases</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Customers with an Unresolved Issue</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4630,7 +4414,7 @@
               <color rgb="001E7B34"/>
               <sz val="10"/>
             </rPr>
-            <t>≥ target</t>
+            <t>≤ target</t>
           </r>
           <r>
             <rPr>
@@ -4647,82 +4431,82 @@
               <color rgb="00C00000"/>
               <sz val="10"/>
             </rPr>
-            <t>&gt; 10% below</t>
-          </r>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
+            <t>&gt; 10% above</t>
+          </r>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="10" t="n">
-        <v>0</v>
+      <c r="E8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="11" t="n">
-        <v>0</v>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" s="14" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -4739,10 +4523,10 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:N7">
     <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="1">
-      <formula>AND(COUNT(F7,F6)=2,F7&gt;=F6)</formula>
+      <formula>AND(COUNT(F7,F6)=2,F7&lt;=F6)</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
-      <formula>AND(COUNT(F7,F6)=2,F7&gt;=0.9*F6)</formula>
+      <formula>AND(COUNT(F7,F6)=2,F7&lt;=1.1*F6)</formula>
     </cfRule>
     <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
       <formula>COUNT(F7,F6)=2</formula>
@@ -4750,10 +4534,10 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="F9:N9">
     <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
-      <formula>AND(COUNT(F9,F8)=2,F9&gt;=F8)</formula>
+      <formula>AND(COUNT(F9,F8)=2,F9&lt;=F8)</formula>
     </cfRule>
     <cfRule type="expression" priority="8" dxfId="1" stopIfTrue="1">
-      <formula>AND(COUNT(F9,F8)=2,F9&gt;=0.9*F8)</formula>
+      <formula>AND(COUNT(F9,F8)=2,F9&lt;=1.1*F8)</formula>
     </cfRule>
     <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
       <formula>COUNT(F9,F8)=2</formula>
@@ -4764,6 +4548,572 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Widget</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Green / Red</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>06-Mar</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>27-Feb</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>20-Feb</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>13-Feb</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>06-Feb</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>30-Jan</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>23-Jan</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>16-Jan</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>09-Jan</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>02-Jan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Development Capacity</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <i val="1"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t>not graded</t>
+          </r>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F2" s="21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G2" s="21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H2" s="21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I2" s="21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J2" s="21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K2" s="21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L2" s="21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M2" s="21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N2" s="21" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>monitor</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G3" s="22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H3" s="22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I3" s="22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J3" s="22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K3" s="22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L3" s="22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M3" s="22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N3" s="22" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Releases Shipped that Meet Acceptance</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>≥ target</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  /  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>&gt; 10% below</t>
+          </r>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Product Releases</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>≥ target</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  /  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>&gt; 10% below</t>
+          </r>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Quality Releases</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="001E7B34"/>
+              <sz val="10"/>
+            </rPr>
+            <t>≥ target</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <color rgb="00808080"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">  /  </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Arial"/>
+              <b val="1"/>
+              <color rgb="00C00000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>&gt; 10% below</t>
+          </r>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F5:N5">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>AND(COUNT(F5,F4)=2,F5&gt;=F4)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
+      <formula>AND(COUNT(F5,F4)=2,F5&gt;=0.9*F4)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>COUNT(F5,F4)=2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:N7">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="1">
+      <formula>AND(COUNT(F7,F6)=2,F7&gt;=F6)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
+      <formula>AND(COUNT(F7,F6)=2,F7&gt;=0.9*F6)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="1">
+      <formula>COUNT(F7,F6)=2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9:N9">
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
+      <formula>AND(COUNT(F9,F8)=2,F9&gt;=F8)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="1" stopIfTrue="1">
+      <formula>AND(COUNT(F9,F8)=2,F9&gt;=0.9*F8)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="9" dxfId="2" stopIfTrue="1">
+      <formula>COUNT(F9,F8)=2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4789,89 +5139,89 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Widget</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Green / Red</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>06-Mar</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>27-Feb</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>20-Feb</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>13-Feb</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>06-Feb</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>30-Jan</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>23-Jan</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>16-Jan</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>09-Jan</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>02-Jan</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Revenue Billed</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4901,88 +5251,88 @@
           </r>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E2" s="12" t="n">
+      <c r="E2" s="15" t="n">
         <v>243880</v>
       </c>
-      <c r="F2" s="12" t="n">
+      <c r="F2" s="15" t="n">
         <v>261808</v>
       </c>
-      <c r="G2" s="12" t="n">
+      <c r="G2" s="15" t="n">
         <v>261808</v>
       </c>
-      <c r="H2" s="12" t="n">
+      <c r="H2" s="15" t="n">
         <v>261808</v>
       </c>
-      <c r="I2" s="12" t="n">
+      <c r="I2" s="15" t="n">
         <v>261808</v>
       </c>
-      <c r="J2" s="12" t="n">
+      <c r="J2" s="15" t="n">
         <v>212821</v>
       </c>
-      <c r="K2" s="12" t="n">
+      <c r="K2" s="15" t="n">
         <v>212821</v>
       </c>
-      <c r="L2" s="12" t="n">
+      <c r="L2" s="15" t="n">
         <v>212821</v>
       </c>
-      <c r="M2" s="12" t="n">
+      <c r="M2" s="15" t="n">
         <v>212821</v>
       </c>
-      <c r="N2" s="12" t="n">
+      <c r="N2" s="15" t="n">
         <v>170257</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="n"/>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="13" t="n">
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="16" t="n">
         <v>258740</v>
       </c>
-      <c r="G3" s="13" t="n">
+      <c r="G3" s="16" t="n">
         <v>261354</v>
       </c>
-      <c r="H3" s="13" t="n">
+      <c r="H3" s="16" t="n">
         <v>256127</v>
       </c>
-      <c r="I3" s="13" t="n">
+      <c r="I3" s="16" t="n">
         <v>261354</v>
       </c>
-      <c r="J3" s="13" t="n">
+      <c r="J3" s="16" t="n">
         <v>212821</v>
       </c>
-      <c r="K3" s="13" t="n">
+      <c r="K3" s="16" t="n">
         <v>214949</v>
       </c>
-      <c r="L3" s="13" t="n">
+      <c r="L3" s="16" t="n">
         <v>210693</v>
       </c>
-      <c r="M3" s="13" t="n">
+      <c r="M3" s="16" t="n">
         <v>212821</v>
       </c>
-      <c r="N3" s="13" t="n">
+      <c r="N3" s="16" t="n">
         <v>170257</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Cash Collected</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5012,88 +5362,88 @@
           </r>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="15" t="n">
         <v>238007</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="15" t="n">
         <v>255386</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="15" t="n">
         <v>255386</v>
       </c>
-      <c r="H4" s="12" t="n">
+      <c r="H4" s="15" t="n">
         <v>255386</v>
       </c>
-      <c r="I4" s="12" t="n">
+      <c r="I4" s="15" t="n">
         <v>255386</v>
       </c>
-      <c r="J4" s="12" t="n">
+      <c r="J4" s="15" t="n">
         <v>207500</v>
       </c>
-      <c r="K4" s="12" t="n">
+      <c r="K4" s="15" t="n">
         <v>207500</v>
       </c>
-      <c r="L4" s="12" t="n">
+      <c r="L4" s="15" t="n">
         <v>207500</v>
       </c>
-      <c r="M4" s="12" t="n">
+      <c r="M4" s="15" t="n">
         <v>207500</v>
       </c>
-      <c r="N4" s="12" t="n">
+      <c r="N4" s="15" t="n">
         <v>166000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="13" t="n">
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="16" t="n">
         <v>253426</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="16" t="n">
         <v>248201</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="16" t="n">
         <v>258651</v>
       </c>
-      <c r="I5" s="13" t="n">
+      <c r="I5" s="16" t="n">
         <v>261264</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="16" t="n">
         <v>207500</v>
       </c>
-      <c r="K5" s="13" t="n">
+      <c r="K5" s="16" t="n">
         <v>207500</v>
       </c>
-      <c r="L5" s="13" t="n">
+      <c r="L5" s="16" t="n">
         <v>207500</v>
       </c>
-      <c r="M5" s="13" t="n">
+      <c r="M5" s="16" t="n">
         <v>207500</v>
       </c>
-      <c r="N5" s="13" t="n">
+      <c r="N5" s="16" t="n">
         <v>166000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Payments Made</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5123,77 +5473,77 @@
           </r>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>target</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="15" t="n">
         <v>233839</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="15" t="n">
         <v>256750</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="15" t="n">
         <v>256750</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="15" t="n">
         <v>256750</v>
       </c>
-      <c r="I6" s="12" t="n">
+      <c r="I6" s="15" t="n">
         <v>256750</v>
       </c>
-      <c r="J6" s="12" t="n">
+      <c r="J6" s="15" t="n">
         <v>213565</v>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" s="15" t="n">
         <v>213565</v>
       </c>
-      <c r="L6" s="12" t="n">
+      <c r="L6" s="15" t="n">
         <v>213565</v>
       </c>
-      <c r="M6" s="12" t="n">
+      <c r="M6" s="15" t="n">
         <v>213565</v>
       </c>
-      <c r="N6" s="12" t="n">
+      <c r="N6" s="15" t="n">
         <v>170852</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>actual</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="13" t="n">
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="16" t="n">
         <v>253377</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="16" t="n">
         <v>250868</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="16" t="n">
         <v>255886</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="I7" s="16" t="n">
         <v>250868</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="16" t="n">
         <v>214010</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K7" s="16" t="n">
         <v>214010</v>
       </c>
-      <c r="L7" s="13" t="n">
+      <c r="L7" s="16" t="n">
         <v>211870</v>
       </c>
-      <c r="M7" s="13" t="n">
+      <c r="M7" s="16" t="n">
         <v>214010</v>
       </c>
-      <c r="N7" s="13" t="n">
+      <c r="N7" s="16" t="n">
         <v>171208</v>
       </c>
     </row>
